--- a/dataset/construct/dataset_splits/data_size/5_percent/merged/fold2.xlsx
+++ b/dataset/construct/dataset_splits/data_size/5_percent/merged/fold2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2583</v>
+        <v>922</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,82 +625,82 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>85.0467322926965</v>
+        <v>75.0324815258448</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>26.4721074380165</v>
       </c>
       <c r="E2" t="n">
-        <v>26.2975778546712</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="I2" t="n">
-        <v>1320</v>
+        <v>391</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
       <c r="K2" t="n">
-        <v>664</v>
+        <v>977</v>
       </c>
       <c r="L2" t="n">
-        <v>401</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
-        <v>318</v>
+        <v>31</v>
       </c>
       <c r="N2" t="n">
-        <v>1383</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>7</v>
+        <v>26.5</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>0.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>27.3745861981156</v>
       </c>
       <c r="X2" t="n">
-        <v>24.65</v>
+        <v>26.7218716216114</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.220216606498195</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.8281130634072</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>24.3439993862133</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -724,39 +709,28 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>154</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2257</v>
+        <v>452</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -764,77 +738,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>68.1240494207418</v>
+        <v>75.6426521345096</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>31.4359113034072</v>
       </c>
       <c r="E3" t="n">
-        <v>24.4897959183673</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>679</v>
+      </c>
+      <c r="I3" t="n">
+        <v>324</v>
+      </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="K3" t="n">
-        <v>338.1</v>
+        <v>1087</v>
       </c>
       <c r="L3" t="n">
-        <v>245.5</v>
+        <v>18.7</v>
       </c>
       <c r="M3" t="n">
-        <v>290.6</v>
+        <v>27</v>
       </c>
       <c r="N3" t="n">
-        <v>874.2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>61.6</v>
+        <v>45.7</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>75.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>24.0641711229947</v>
       </c>
       <c r="X3" t="n">
-        <v>27.65</v>
+        <v>23.2857506244092</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.16887417218543</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.2154316271963</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.9211850934372</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -861,24 +837,15 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>138</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54470472</v>
+        <v>52919815</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,74 +853,88 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>89.39630390143741</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>79.49349760438059</v>
+      </c>
+      <c r="D4" t="n">
+        <v>22.8373702422145</v>
+      </c>
       <c r="E4" t="n">
-        <v>27.9903628117914</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>60</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>41</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="I4" t="n">
+        <v>146</v>
+      </c>
       <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>227</v>
+      </c>
+      <c r="K4" t="n">
+        <v>673</v>
+      </c>
+      <c r="L4" t="n">
+        <v>294</v>
+      </c>
+      <c r="M4" t="n">
+        <v>33</v>
+      </c>
+      <c r="N4" t="n">
+        <v>39</v>
+      </c>
       <c r="O4" t="n">
-        <v>518</v>
+        <v>366</v>
       </c>
       <c r="P4" t="n">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>349</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1356</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>0.26</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>23.74591750931078</v>
       </c>
       <c r="X4" t="n">
-        <v>26.9</v>
+        <v>22.84236339419522</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>88.5</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>597</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -970,25 +951,12 @@
       <c r="AI4" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>138</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>110</v>
-      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>52511121</v>
+        <v>54990446</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -996,117 +964,106 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>84.0876112251882</v>
+        <v>79.17590691307321</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>29.8605512257756</v>
       </c>
       <c r="E5" t="n">
-        <v>29.1363163371488</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>40</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>419</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>439</v>
+        <v>141</v>
       </c>
       <c r="M5" t="n">
-        <v>314</v>
+        <v>116</v>
       </c>
       <c r="N5" t="n">
-        <v>1173</v>
+        <v>82</v>
       </c>
       <c r="O5" t="n">
-        <v>419</v>
+        <v>339</v>
       </c>
       <c r="P5" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1139</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>221</v>
+        <v>30.4</v>
       </c>
       <c r="V5" t="n">
-        <v>394</v>
+        <v>0.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>30.08028424436822</v>
       </c>
       <c r="X5" t="n">
-        <v>28.8</v>
+        <v>29.51741554510272</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>90.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>629.2</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>128</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>52011910</v>
+        <v>52772610</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1114,105 +1071,110 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>80.8980150581793</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>82.2313483915127</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24.3417582863402</v>
+      </c>
       <c r="E6" t="n">
-        <v>16.5289256198347</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>35</v>
+      </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>622</v>
+      </c>
+      <c r="I6" t="n">
+        <v>632</v>
+      </c>
       <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>653</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1907</v>
+      </c>
+      <c r="L6" t="n">
+        <v>622</v>
+      </c>
+      <c r="M6" t="n">
+        <v>431</v>
+      </c>
+      <c r="N6" t="n">
+        <v>622</v>
+      </c>
       <c r="O6" t="n">
-        <v>340.14984</v>
+        <v>1675</v>
       </c>
       <c r="P6" t="n">
-        <v>38.76126</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>32.43289</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>411.34402</v>
+        <v>88</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>31.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>32.34028443627313</v>
       </c>
       <c r="X6" t="n">
-        <v>21.753738</v>
+        <v>30.52886088189566</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>69.67747</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>371.27145</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55642168</v>
+        <v>54767222</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1220,77 +1182,83 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>82.4695414099932</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>82.7186858316222</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27.7322997761369</v>
+      </c>
       <c r="E7" t="n">
-        <v>24.5778671518401</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>56</v>
+      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
-        <v>55</v>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>428</v>
+      </c>
+      <c r="M7" t="n">
+        <v>123</v>
+      </c>
+      <c r="N7" t="n">
+        <v>143</v>
+      </c>
       <c r="O7" t="n">
-        <v>435.7692</v>
+        <v>694</v>
       </c>
       <c r="P7" t="n">
-        <v>471.15186</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>348.57095</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1255.492</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>175</v>
+        <v>27.7</v>
       </c>
       <c r="V7" t="n">
-        <v>226</v>
+        <v>0.21</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>27.69296009798979</v>
       </c>
       <c r="X7" t="n">
-        <v>27.29889</v>
+        <v>27.27785163723912</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>86.90398999999999</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>573.0519</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1299,30 +1267,21 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>148</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>53959319</v>
+        <v>51549417</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1330,70 +1289,82 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>82.8637919233402</v>
+        <v>69.864476386037</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>24.2122933884297</v>
       </c>
       <c r="E8" t="n">
-        <v>24.7251829329413</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>48</v>
+      </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>55</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>781</v>
+      </c>
+      <c r="I8" t="n">
+        <v>641</v>
+      </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>735</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2157</v>
+      </c>
+      <c r="L8" t="n">
+        <v>774</v>
+      </c>
+      <c r="M8" t="n">
+        <v>351</v>
+      </c>
+      <c r="N8" t="n">
+        <v>595</v>
+      </c>
       <c r="O8" t="n">
-        <v>331</v>
+        <v>1720</v>
       </c>
       <c r="P8" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>28.17042492726548</v>
       </c>
       <c r="X8" t="n">
-        <v>24.1</v>
+        <v>27.44305359669089</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>79.8</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>471.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1402,39 +1373,30 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>145</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>52714540</v>
+        <v>54514630</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1442,77 +1404,71 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>82.2313483915127</v>
+        <v>82.2915811088296</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>27.8851873884593</v>
       </c>
       <c r="E9" t="n">
-        <v>30.7933824417341</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>402</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="M9" t="n">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="N9" t="n">
-        <v>833</v>
+        <v>131</v>
       </c>
       <c r="O9" t="n">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="P9" t="n">
-        <v>175</v>
+        <v>33</v>
       </c>
       <c r="Q9" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>833</v>
+        <v>102</v>
       </c>
       <c r="S9" t="n">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="V9" t="n">
-        <v>36</v>
+        <v>0.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>24.06422739549457</v>
       </c>
       <c r="X9" t="n">
-        <v>30.4</v>
+        <v>23.49902105517675</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>98.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>700.4</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1530,28 +1486,19 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>127</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>151</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
